--- a/rsvp_forms/012_engagement_party_rsvp_survey--rsvp_forms.xlsx
+++ b/rsvp_forms/012_engagement_party_rsvp_survey--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>guest_attendance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>Guest attendance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>guest_attendance</t>
+          <t>dietary_preferences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>guest_attendance</t>
+          <t>Dietary preferences</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dietary_preferences</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dietary_preferences</t>
+          <t>Additional notes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,46 +584,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>rsvp_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>RSVP date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rsvp_date</t>
+          <t>will_attend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rsvp_date</t>
+          <t>Will attend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>will_attend</t>
+          <t>will_dine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>will_attend</t>
+          <t>Will dine</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,58 +658,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>will_dine</t>
+          <t>will_work</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>will_dine</t>
+          <t>Will work</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>will_work</t>
+          <t>rsvp_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>will_work</t>
+          <t>RSVP time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rsvp_time</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rsvp_time</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,35 +750,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>guest_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Guest name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>guest_name</t>
+          <t>guest_relation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>guest_name</t>
+          <t>Guest relation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>guest_relation</t>
+          <t>guest_message</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>guest_relation</t>
+          <t>Guest message</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,223 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>guest_message</t>
+          <t>host_message</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>guest_message</t>
+          <t>Host message</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>host_message</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>host_message</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>guest_message</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>host_message</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rsvp_time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>guest_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>guest_name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>guest_message</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>guest_message</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>host_message</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>host_message</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
